--- a/data/24Maj-Oaks-v-Tigers.xlsx
+++ b/data/24Maj-Oaks-v-Tigers.xlsx
@@ -259,7 +259,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:O159"/>
   <sheetData>
     <row r="1">
@@ -539,8 +539,10 @@
       <c r="D25" t="s">
         <v>25</v>
       </c>
-      <c r="E25" t="s">
-        <v>26</v>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>DI</t>
+        </is>
       </c>
       <c r="I25" t="s">
         <v>18</v>
@@ -1067,8 +1069,10 @@
       <c r="D76" t="s">
         <v>16</v>
       </c>
-      <c r="E76" t="s">
-        <v>47</v>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>LCDN</t>
+        </is>
       </c>
       <c r="F76" t="s">
         <v>48</v>
@@ -1213,8 +1217,10 @@
       <c r="D86" t="s">
         <v>16</v>
       </c>
-      <c r="E86" t="s">
-        <v>58</v>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
       </c>
       <c r="I86" t="s">
         <v>18</v>
@@ -1788,8 +1794,10 @@
       <c r="D141" t="s">
         <v>22</v>
       </c>
-      <c r="E141" t="s">
-        <v>73</v>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>DGLG</t>
+        </is>
       </c>
       <c r="I141" t="s">
         <v>18</v>
@@ -1830,8 +1838,10 @@
       <c r="D144" t="s">
         <v>16</v>
       </c>
-      <c r="E144" t="s">
-        <v>58</v>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
       </c>
       <c r="I144" t="s">
         <v>29</v>
